--- a/data/trending_integrated_20260921_11.xlsx
+++ b/data/trending_integrated_20260921_11.xlsx
@@ -578,13 +578,13 @@
         <v>-0.04</v>
       </c>
       <c r="E2" t="n">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="F2" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G2" t="n">
-        <v>230</v>
+        <v>252</v>
       </c>
       <c r="H2" t="n">
         <v>0.35</v>
@@ -610,7 +610,7 @@
         <v>0.39</v>
       </c>
       <c r="O2" t="n">
-        <v>194511612785</v>
+        <v>196299489535</v>
       </c>
       <c r="P2" t="n">
         <v>39350</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>미국 타임지 선정 '세계 최고 헬스테크 기업' 그룹 편입 소식. 2주간의 급락 이후 반등 및 상한가 기록.</t>
+          <t>미국 타임지 선정 '세계 최고 헬스테크 기업' 그룹 편입. 단기 반등 및 추가 상승 기대.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['헬스테크', '타임지 선정', '반등']</t>
+          <t>['헬스테크', '기업 선정', '타임지']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11000</v>
+        <v>10950</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+21.95%</t>
+          <t>'+21.40%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.09</v>
       </c>
       <c r="E3" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F3" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G3" t="n">
-        <v>130</v>
+        <v>161</v>
       </c>
       <c r="H3" t="n">
         <v>8.6</v>
@@ -693,7 +693,7 @@
         <v>9050</v>
       </c>
       <c r="L3" t="n">
-        <v>11050</v>
+        <v>11080</v>
       </c>
       <c r="M3" t="n">
         <v>9010</v>
@@ -702,7 +702,7 @@
         <v>8.51</v>
       </c>
       <c r="O3" t="n">
-        <v>177993523400</v>
+        <v>189440275690</v>
       </c>
       <c r="P3" t="n">
         <v>11640</v>
@@ -711,7 +711,7 @@
         <v>3735</v>
       </c>
       <c r="R3" t="n">
-        <v>165000</v>
+        <v>405000</v>
       </c>
       <c r="S3" t="n">
         <v>52000</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5830</v>
+        <v>5870</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+7.37%</t>
+          <t>'+8.10%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.31</v>
       </c>
       <c r="E4" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F4" t="n">
         <v>31</v>
       </c>
       <c r="G4" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="H4" t="n">
         <v>0.19</v>
@@ -794,7 +794,7 @@
         <v>0.5</v>
       </c>
       <c r="O4" t="n">
-        <v>56544640025</v>
+        <v>57187086200</v>
       </c>
       <c r="P4" t="n">
         <v>13140</v>
@@ -854,13 +854,13 @@
         <v>-0.48</v>
       </c>
       <c r="E5" t="n">
-        <v>290</v>
+        <v>306</v>
       </c>
       <c r="F5" t="n">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="G5" t="n">
-        <v>1259</v>
+        <v>1326</v>
       </c>
       <c r="H5" t="n">
         <v>16.67</v>
@@ -886,7 +886,7 @@
         <v>17.15</v>
       </c>
       <c r="O5" t="n">
-        <v>22369579875</v>
+        <v>22826737075</v>
       </c>
       <c r="P5" t="n">
         <v>69200</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 FDA 신약 승인 과정에서 제품명 조건부 수용 관련 논란. 담관암 치료제 리보세라닙 기대감과 회의론 공존.</t>
+          <t>신약 승인 관련 기대감과 불확실성 혼재. 조건부 승인 여부 및 임상 결과 주목.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['FDA 승인', '리보세라닙', '담관암']</t>
+          <t>['신약 승인', 'FDA', '임상 결과']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>207000</v>
+        <v>11110</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+5.56%</t>
+          <t>'+5.61%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.09</v>
+        <v>0.16</v>
       </c>
       <c r="E6" t="n">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="F6" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="G6" t="n">
-        <v>228</v>
+        <v>159</v>
       </c>
       <c r="H6" t="n">
-        <v>75.44</v>
+        <v>18.29</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,38 +963,38 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>196100</v>
+        <v>10520</v>
       </c>
       <c r="K6" t="n">
-        <v>199800</v>
+        <v>10780</v>
       </c>
       <c r="L6" t="n">
-        <v>207500</v>
+        <v>12190</v>
       </c>
       <c r="M6" t="n">
-        <v>199600</v>
+        <v>10590</v>
       </c>
       <c r="N6" t="n">
-        <v>75.53</v>
+        <v>18.13</v>
       </c>
       <c r="O6" t="n">
-        <v>469557000300</v>
+        <v>162268259620</v>
       </c>
       <c r="P6" t="n">
-        <v>243500</v>
+        <v>22450</v>
       </c>
       <c r="Q6" t="n">
-        <v>64700</v>
+        <v>1760</v>
       </c>
       <c r="R6" t="n">
-        <v>504000</v>
+        <v>-6000</v>
       </c>
       <c r="S6" t="n">
-        <v>-25000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>삼성전자우, 배당 기대감 속 주가 상승 전망. 자사주 취득 및 소각, 외인 매수세 유입 가능성 언급.</t>
+          <t>미국 광통신주 급등에 영향을 받으며 국내 증시도 동반 상승 기대. 그러나 개인 투자자들의 매도 심리 및 차익 실현 매물 출현 가능성으로 단기적인 조정 우려. 높은 변동성 속 신중한 접근 필요.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,11 +1003,11 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['배당', '자사주', '외인']</t>
+          <t>['광통신', '추세', '변동성']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11060</v>
+        <v>206500</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+5.13%</t>
+          <t>'+5.30%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.16</v>
+        <v>-0.09</v>
       </c>
       <c r="E7" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="F7" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="G7" t="n">
-        <v>144</v>
+        <v>228</v>
       </c>
       <c r="H7" t="n">
-        <v>18.29</v>
+        <v>75.44</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,38 +1055,38 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>10520</v>
+        <v>196100</v>
       </c>
       <c r="K7" t="n">
-        <v>10780</v>
+        <v>199800</v>
       </c>
       <c r="L7" t="n">
-        <v>12190</v>
+        <v>207500</v>
       </c>
       <c r="M7" t="n">
-        <v>10590</v>
+        <v>199600</v>
       </c>
       <c r="N7" t="n">
-        <v>18.13</v>
+        <v>75.53</v>
       </c>
       <c r="O7" t="n">
-        <v>161463031405</v>
+        <v>479770360300</v>
       </c>
       <c r="P7" t="n">
-        <v>22450</v>
+        <v>243500</v>
       </c>
       <c r="Q7" t="n">
-        <v>1760</v>
+        <v>64700</v>
       </c>
       <c r="R7" t="n">
-        <v>-6000</v>
+        <v>504000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-25000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 광통신주 급등에 영향을 받으며 국내 증시도 동반 상승 기대. 그러나 개인 투자자들의 매도 심리 및 차익 실현 매물 출현 가능성으로 단기적인 조정 우려. 높은 변동성 속 신중한 접근 필요.</t>
+          <t>삼성전자우, 배당 기대감 속 주가 상승 전망. 자사주 취득 및 소각, 외인 매수세 유입 가능성 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,11 +1095,11 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['광통신', '추세', '변동성']</t>
+          <t>['배당', '자사주', '외인']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
@@ -1130,13 +1130,13 @@
         <v>-0.02</v>
       </c>
       <c r="E8" t="n">
-        <v>790</v>
+        <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="G8" t="n">
-        <v>3217</v>
+        <v>3140</v>
       </c>
       <c r="H8" t="n">
         <v>46.46</v>
@@ -1162,7 +1162,7 @@
         <v>46.48</v>
       </c>
       <c r="O8" t="n">
-        <v>2569216309000</v>
+        <v>2658912840500</v>
       </c>
       <c r="P8" t="n">
         <v>374500</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>삼성전자, 내년 상반기 상승장 전망 속 일부 증권사 앱 먹통 문제 발생. 배당 및 AI 감속론 관련 언급.</t>
+          <t>AI 감속론 부인 및 28만원 안착 전망. 10월 8일경 3분기 실적 발표 및 4분기 자사주 소각/배당 예정.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['AI', '배당', '전망']</t>
+          <t>['AI', '실적 발표', '자사주 소각']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1869000</v>
+        <v>1870000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+0.65%</t>
+          <t>'+0.70%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.13</v>
       </c>
       <c r="E9" t="n">
-        <v>786</v>
+        <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>461</v>
+        <v>470</v>
       </c>
       <c r="G9" t="n">
-        <v>3061</v>
+        <v>2949</v>
       </c>
       <c r="H9" t="n">
         <v>50.23</v>
@@ -1254,7 +1254,7 @@
         <v>50.1</v>
       </c>
       <c r="O9" t="n">
-        <v>2188879784500</v>
+        <v>2267211999000</v>
       </c>
       <c r="P9" t="n">
         <v>2987000</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 증시 반도체주 급등 및 HBM 시장 성장 전망. 20만원 돌파 및 분기 사상 최고 영업이익 예상.</t>
+          <t>반도체 시장 성장 및 AI 수요 증가 전망. 3분기 역대 최고 영업이익 예상.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['SK하이닉스', 'HBM', '반도체']</t>
+          <t>['반도체 시장', 'AI 수요', '영업이익']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>26900</v>
+        <v>26850</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.37%</t>
+          <t>'+0.19%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.3</v>
       </c>
       <c r="E10" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F10" t="n">
         <v>36</v>
       </c>
       <c r="G10" t="n">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="H10" t="n">
         <v>2.11</v>
@@ -1346,7 +1346,7 @@
         <v>2.41</v>
       </c>
       <c r="O10" t="n">
-        <v>97912177100</v>
+        <v>99925119875</v>
       </c>
       <c r="P10" t="n">
         <v>59600</v>
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13670</v>
+        <v>4175</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-1.44%</t>
+          <t>'-1.07%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.58</v>
+        <v>-0.22</v>
       </c>
       <c r="E11" t="n">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="F11" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="G11" t="n">
-        <v>263</v>
+        <v>198</v>
       </c>
       <c r="H11" t="n">
-        <v>5.5</v>
+        <v>0.33</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,38 +1423,38 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>13870</v>
+        <v>4220</v>
       </c>
       <c r="K11" t="n">
-        <v>14070</v>
+        <v>4220</v>
       </c>
       <c r="L11" t="n">
-        <v>14790</v>
+        <v>4415</v>
       </c>
       <c r="M11" t="n">
-        <v>13660</v>
+        <v>4105</v>
       </c>
       <c r="N11" t="n">
-        <v>4.92</v>
+        <v>0.55</v>
       </c>
       <c r="O11" t="n">
-        <v>56086868565</v>
+        <v>26464192658</v>
       </c>
       <c r="P11" t="n">
-        <v>30200</v>
+        <v>6480</v>
       </c>
       <c r="Q11" t="n">
-        <v>3540</v>
+        <v>1738</v>
       </c>
       <c r="R11" t="n">
-        <v>-298000</v>
+        <v>208000</v>
       </c>
       <c r="S11" t="n">
-        <v>-7000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>원전 관련 기대감 언급. 신한투자증권의 공매도 의혹 및 주가 하락에 대한 불만.</t>
+          <t>미투온, 미버스 관련 코인주 동반 상승 속 거래량 부진 및 재료 소멸 우려. 매도 물량 출회 가능성.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['원전', '신한투자증권', '공매도']</t>
+          <t>['미버스', '거래량', '재료소멸']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,191 +1476,191 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>201490</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>78600</v>
+        <v>13720</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.75%</t>
+          <t>'-1.08%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.1</v>
+        <v>0.58</v>
       </c>
       <c r="E12" t="n">
-        <v>131</v>
+        <v>51</v>
       </c>
       <c r="F12" t="n">
-        <v>74</v>
+        <v>32</v>
       </c>
       <c r="G12" t="n">
-        <v>601</v>
+        <v>286</v>
       </c>
       <c r="H12" t="n">
-        <v>10.58</v>
+        <v>5.5</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>80000</v>
+        <v>13870</v>
       </c>
       <c r="K12" t="n">
-        <v>82900</v>
+        <v>14070</v>
       </c>
       <c r="L12" t="n">
-        <v>83000</v>
+        <v>14790</v>
       </c>
       <c r="M12" t="n">
-        <v>75300</v>
+        <v>13610</v>
       </c>
       <c r="N12" t="n">
-        <v>10.68</v>
+        <v>4.92</v>
       </c>
       <c r="O12" t="n">
-        <v>82886633900</v>
+        <v>57713648365</v>
       </c>
       <c r="P12" t="n">
-        <v>184000</v>
+        <v>30200</v>
       </c>
       <c r="Q12" t="n">
-        <v>44750</v>
+        <v>3540</v>
       </c>
       <c r="R12" t="n">
-        <v>-499000</v>
+        <v>-298000</v>
       </c>
       <c r="S12" t="n">
-        <v>-56000</v>
+        <v>-7000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>유럽 드론 시장 관련 K-방산 뉴스에 따른 기대감. 공매도 세력에 대한 비판 및 공매도 금지 요구.</t>
+          <t>원전 관련 기대감 언급. 신한투자증권의 공매도 의혹 및 주가 하락에 대한 불만.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['K-방산', '드론', '공매도']</t>
+          <t>['원전', '신한투자증권', '공매도']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>272210</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>한화시스템</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4130</v>
+        <v>78800</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-2.13%</t>
+          <t>'-1.50%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.22</v>
+        <v>-0.1</v>
       </c>
       <c r="E13" t="n">
-        <v>66</v>
+        <v>133</v>
       </c>
       <c r="F13" t="n">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="G13" t="n">
-        <v>189</v>
+        <v>603</v>
       </c>
       <c r="H13" t="n">
-        <v>0.33</v>
+        <v>10.58</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>4220</v>
+        <v>80000</v>
       </c>
       <c r="K13" t="n">
-        <v>4220</v>
+        <v>82900</v>
       </c>
       <c r="L13" t="n">
-        <v>4415</v>
+        <v>83000</v>
       </c>
       <c r="M13" t="n">
-        <v>4120</v>
+        <v>75300</v>
       </c>
       <c r="N13" t="n">
-        <v>0.55</v>
+        <v>10.68</v>
       </c>
       <c r="O13" t="n">
-        <v>25896756949</v>
+        <v>84724054200</v>
       </c>
       <c r="P13" t="n">
-        <v>6480</v>
+        <v>184000</v>
       </c>
       <c r="Q13" t="n">
-        <v>1738</v>
+        <v>44750</v>
       </c>
       <c r="R13" t="n">
-        <v>208000</v>
+        <v>-499000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-56000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미투온, 미버스 관련 코인주 동반 상승 속 거래량 부진 및 재료 소멸 우려. 매도 물량 출회 가능성.</t>
+          <t>유럽 드론 시장 관련 K-방산 뉴스에 따른 기대감. 공매도 세력에 대한 비판 및 공매도 금지 요구.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['미버스', '거래량', '재료소멸']</t>
+          <t>['K-방산', '드론', '공매도']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>272210</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18220</v>
+        <v>18390</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.65%</t>
+          <t>'-2.75%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F14" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G14" t="n">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="H14" t="n">
         <v>10.74</v>
@@ -1714,7 +1714,7 @@
         <v>10.74</v>
       </c>
       <c r="O14" t="n">
-        <v>53257496090</v>
+        <v>54767800615</v>
       </c>
       <c r="P14" t="n">
         <v>40350</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17650</v>
+        <v>17640</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.66%</t>
+          <t>'-3.71%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>3.29</v>
       </c>
       <c r="E15" t="n">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="F15" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G15" t="n">
-        <v>734</v>
+        <v>764</v>
       </c>
       <c r="H15" t="n">
         <v>7.9</v>
@@ -1806,7 +1806,7 @@
         <v>4.61</v>
       </c>
       <c r="O15" t="n">
-        <v>166729946985</v>
+        <v>168673202835</v>
       </c>
       <c r="P15" t="n">
         <v>31500</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미국 광통신 AI 주 급등 및 관련주 상승 소식에 따른 기대감. 기관 매수세 유입 및 외국인 매도 불가 전망.</t>
+          <t>미국 광통신 AI주 급등세에 따른 연말/연초까지 상승 전망.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['광통신', 'AI 주', '기관 매수']</t>
+          <t>['광통신', 'AI주', '미국 시장']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>30100</v>
+        <v>30150</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.29%</t>
+          <t>'-4.13%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.48</v>
       </c>
       <c r="E16" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G16" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H16" t="n">
         <v>11.92</v>
@@ -1898,7 +1898,7 @@
         <v>11.44</v>
       </c>
       <c r="O16" t="n">
-        <v>61293277100</v>
+        <v>61949155525</v>
       </c>
       <c r="P16" t="n">
         <v>75900</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>312500</v>
+        <v>312000</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.43%</t>
+          <t>'-4.59%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>1.66</v>
       </c>
       <c r="E17" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F17" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G17" t="n">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H17" t="n">
         <v>3.62</v>
@@ -1990,7 +1990,7 @@
         <v>1.96</v>
       </c>
       <c r="O17" t="n">
-        <v>70019172750</v>
+        <v>70657171750</v>
       </c>
       <c r="P17" t="n">
         <v>635000</v>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>27200</v>
+        <v>26900</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-27.27%</t>
+          <t>'-28.07%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.01</v>
       </c>
       <c r="E18" t="n">
-        <v>558</v>
+        <v>575</v>
       </c>
       <c r="F18" t="n">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="G18" t="n">
-        <v>1078</v>
+        <v>1091</v>
       </c>
       <c r="H18" t="n">
         <v>7.09</v>
@@ -2082,7 +2082,7 @@
         <v>7.08</v>
       </c>
       <c r="O18" t="n">
-        <v>69630959500</v>
+        <v>70839450750</v>
       </c>
       <c r="P18" t="n">
         <v>146600</v>

--- a/data/trending_integrated_20260921_11.xlsx
+++ b/data/trending_integrated_20260921_11.xlsx
@@ -578,13 +578,13 @@
         <v>-0.04</v>
       </c>
       <c r="E2" t="n">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="F2" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G2" t="n">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="H2" t="n">
         <v>0.35</v>
@@ -610,7 +610,7 @@
         <v>0.39</v>
       </c>
       <c r="O2" t="n">
-        <v>196299489535</v>
+        <v>201912589785</v>
       </c>
       <c r="P2" t="n">
         <v>39350</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>미국 타임지 선정 '세계 최고 헬스테크 기업' 그룹 편입. 단기 반등 및 추가 상승 기대.</t>
+          <t>美 타임 선정 '세계 최고 헬스테크 기업' 선정, 2주간의 폭락 후 반등 기대. 기관/외인 매수세 확인.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['헬스테크', '기업 선정', '타임지']</t>
+          <t>['헬스테크', '타임지', '반등']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,11 +659,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10950</v>
+        <v>10820</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+21.40%</t>
+          <t>'+19.96%</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -676,7 +676,7 @@
         <v>51</v>
       </c>
       <c r="G3" t="n">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="H3" t="n">
         <v>8.6</v>
@@ -702,7 +702,7 @@
         <v>8.51</v>
       </c>
       <c r="O3" t="n">
-        <v>189440275690</v>
+        <v>195383117490</v>
       </c>
       <c r="P3" t="n">
         <v>11640</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5870</v>
+        <v>5930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+8.10%</t>
+          <t>'+9.21%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.31</v>
       </c>
       <c r="E4" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F4" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G4" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H4" t="n">
         <v>0.19</v>
@@ -794,7 +794,7 @@
         <v>0.5</v>
       </c>
       <c r="O4" t="n">
-        <v>57187086200</v>
+        <v>57928444150</v>
       </c>
       <c r="P4" t="n">
         <v>13140</v>
@@ -839,83 +839,83 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31450</v>
+        <v>11180</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+6.07%</t>
+          <t>'+6.27%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.48</v>
+        <v>0.16</v>
       </c>
       <c r="E5" t="n">
-        <v>306</v>
+        <v>82</v>
       </c>
       <c r="F5" t="n">
-        <v>198</v>
+        <v>55</v>
       </c>
       <c r="G5" t="n">
-        <v>1326</v>
+        <v>164</v>
       </c>
       <c r="H5" t="n">
-        <v>16.67</v>
+        <v>18.29</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>29650</v>
+        <v>10520</v>
       </c>
       <c r="K5" t="n">
-        <v>30400</v>
+        <v>10780</v>
       </c>
       <c r="L5" t="n">
-        <v>33400</v>
+        <v>12190</v>
       </c>
       <c r="M5" t="n">
-        <v>29400</v>
+        <v>10590</v>
       </c>
       <c r="N5" t="n">
-        <v>17.15</v>
+        <v>18.13</v>
       </c>
       <c r="O5" t="n">
-        <v>22826737075</v>
+        <v>164409880460</v>
       </c>
       <c r="P5" t="n">
-        <v>69200</v>
+        <v>22450</v>
       </c>
       <c r="Q5" t="n">
-        <v>24150</v>
+        <v>1760</v>
       </c>
       <c r="R5" t="n">
-        <v>-148000</v>
+        <v>-6000</v>
       </c>
       <c r="S5" t="n">
-        <v>-7000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>신약 승인 관련 기대감과 불확실성 혼재. 조건부 승인 여부 및 임상 결과 주목.</t>
+          <t>광통신주 미장 급등 및 나스닥 선물 상승 영향, 20% 상승 기대감. 거래량 부족, 개인 물량 털리는 구간 우려.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['신약 승인', 'FDA', '임상 결과']</t>
+          <t>['광통신', '추세', '거래량']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,99 +924,99 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11110</v>
+        <v>31400</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+5.61%</t>
+          <t>'+5.90%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.16</v>
+        <v>-0.48</v>
       </c>
       <c r="E6" t="n">
-        <v>78</v>
+        <v>316</v>
       </c>
       <c r="F6" t="n">
-        <v>54</v>
+        <v>201</v>
       </c>
       <c r="G6" t="n">
-        <v>159</v>
+        <v>1376</v>
       </c>
       <c r="H6" t="n">
-        <v>18.29</v>
+        <v>16.67</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>10520</v>
+        <v>29650</v>
       </c>
       <c r="K6" t="n">
-        <v>10780</v>
+        <v>30400</v>
       </c>
       <c r="L6" t="n">
-        <v>12190</v>
+        <v>33400</v>
       </c>
       <c r="M6" t="n">
-        <v>10590</v>
+        <v>29400</v>
       </c>
       <c r="N6" t="n">
-        <v>18.13</v>
+        <v>17.15</v>
       </c>
       <c r="O6" t="n">
-        <v>162268259620</v>
+        <v>23349090225</v>
       </c>
       <c r="P6" t="n">
-        <v>22450</v>
+        <v>69200</v>
       </c>
       <c r="Q6" t="n">
-        <v>1760</v>
+        <v>24150</v>
       </c>
       <c r="R6" t="n">
-        <v>-6000</v>
+        <v>-148000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-7000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>미국 광통신주 급등에 영향을 받으며 국내 증시도 동반 상승 기대. 그러나 개인 투자자들의 매도 심리 및 차익 실현 매물 출현 가능성으로 단기적인 조정 우려. 높은 변동성 속 신중한 접근 필요.</t>
+          <t>FDA 신약 승인 과정에서 제품명 조건부 수용 관련 내용, 리보세라닙 동일시 우려. 투자자 손실 관련 경고.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['광통신', '추세', '변동성']</t>
+          <t>['FDA', '신약 승인', '리보세라닙']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>206500</v>
+        <v>207000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+5.30%</t>
+          <t>'+5.56%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.09</v>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F7" t="n">
         <v>45</v>
       </c>
       <c r="G7" t="n">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="H7" t="n">
         <v>75.44</v>
@@ -1070,7 +1070,7 @@
         <v>75.53</v>
       </c>
       <c r="O7" t="n">
-        <v>479770360300</v>
+        <v>489922807050</v>
       </c>
       <c r="P7" t="n">
         <v>243500</v>
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>271500</v>
+        <v>272000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.02%</t>
+          <t>'+4.21%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1133,10 +1133,10 @@
         <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="G8" t="n">
-        <v>3140</v>
+        <v>2977</v>
       </c>
       <c r="H8" t="n">
         <v>46.46</v>
@@ -1162,7 +1162,7 @@
         <v>46.48</v>
       </c>
       <c r="O8" t="n">
-        <v>2658912840500</v>
+        <v>2793244119750</v>
       </c>
       <c r="P8" t="n">
         <v>374500</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>AI 감속론 부인 및 28만원 안착 전망. 10월 8일경 3분기 실적 발표 및 4분기 자사주 소각/배당 예정.</t>
+          <t>내년 상반기 상승장 전망, 배당금 및 자사주 소각/배당 관련 기대감. 신한증권 시스템 먹통 관련 불만 제기.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['AI', '실적 발표', '자사주 소각']</t>
+          <t>['AI', '배당', '자사주']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1228,7 +1228,7 @@
         <v>470</v>
       </c>
       <c r="G9" t="n">
-        <v>2949</v>
+        <v>2796</v>
       </c>
       <c r="H9" t="n">
         <v>50.23</v>
@@ -1254,7 +1254,7 @@
         <v>50.1</v>
       </c>
       <c r="O9" t="n">
-        <v>2267211999000</v>
+        <v>2349422774000</v>
       </c>
       <c r="P9" t="n">
         <v>2987000</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>반도체 시장 성장 및 AI 수요 증가 전망. 3분기 역대 최고 영업이익 예상.</t>
+          <t>미선물 및 반도체주 급등, 20일선 위로 상승 추세 전환 기대. 3분기 및 연간 영업이익 증대 전망.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['반도체 시장', 'AI 수요', '영업이익']</t>
+          <t>['반도체', 'AI', '추세']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>26850</v>
+        <v>26550</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.19%</t>
+          <t>'-0.93%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.3</v>
       </c>
       <c r="E10" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F10" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G10" t="n">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="H10" t="n">
         <v>2.11</v>
@@ -1346,7 +1346,7 @@
         <v>2.41</v>
       </c>
       <c r="O10" t="n">
-        <v>99925119875</v>
+        <v>102480519425</v>
       </c>
       <c r="P10" t="n">
         <v>59600</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4175</v>
+        <v>4160</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-1.07%</t>
+          <t>'-1.42%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.22</v>
       </c>
       <c r="E11" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G11" t="n">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="H11" t="n">
         <v>0.33</v>
@@ -1438,7 +1438,7 @@
         <v>0.55</v>
       </c>
       <c r="O11" t="n">
-        <v>26464192658</v>
+        <v>26654188343</v>
       </c>
       <c r="P11" t="n">
         <v>6480</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13720</v>
+        <v>13660</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.08%</t>
+          <t>'-1.51%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.58</v>
       </c>
       <c r="E12" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F12" t="n">
         <v>32</v>
       </c>
       <c r="G12" t="n">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="H12" t="n">
         <v>5.5</v>
@@ -1530,7 +1530,7 @@
         <v>4.92</v>
       </c>
       <c r="O12" t="n">
-        <v>57713648365</v>
+        <v>58381367610</v>
       </c>
       <c r="P12" t="n">
         <v>30200</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>78800</v>
+        <v>78500</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.50%</t>
+          <t>'-1.88%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.1</v>
       </c>
       <c r="E13" t="n">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="F13" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G13" t="n">
-        <v>603</v>
+        <v>611</v>
       </c>
       <c r="H13" t="n">
         <v>10.58</v>
@@ -1622,7 +1622,7 @@
         <v>10.68</v>
       </c>
       <c r="O13" t="n">
-        <v>84724054200</v>
+        <v>86445689350</v>
       </c>
       <c r="P13" t="n">
         <v>184000</v>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>유럽 드론 시장 관련 K-방산 뉴스에 따른 기대감. 공매도 세력에 대한 비판 및 공매도 금지 요구.</t>
+          <t>K-방산, 유럽 드론 시장 진출 기대감. 공매도 규제 및 숏커버링 통한 주가 상승 전망.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18390</v>
+        <v>18420</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-2.75%</t>
+          <t>'-2.59%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F14" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G14" t="n">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="H14" t="n">
         <v>10.74</v>
@@ -1714,7 +1714,7 @@
         <v>10.74</v>
       </c>
       <c r="O14" t="n">
-        <v>54767800615</v>
+        <v>57686796355</v>
       </c>
       <c r="P14" t="n">
         <v>40350</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17640</v>
+        <v>17610</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.71%</t>
+          <t>'-3.88%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>3.29</v>
       </c>
       <c r="E15" t="n">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="F15" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G15" t="n">
-        <v>764</v>
+        <v>780</v>
       </c>
       <c r="H15" t="n">
         <v>7.9</v>
@@ -1806,7 +1806,7 @@
         <v>4.61</v>
       </c>
       <c r="O15" t="n">
-        <v>168673202835</v>
+        <v>172019865590</v>
       </c>
       <c r="P15" t="n">
         <v>31500</v>
@@ -1866,10 +1866,10 @@
         <v>0.48</v>
       </c>
       <c r="E16" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F16" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G16" t="n">
         <v>124</v>
@@ -1898,7 +1898,7 @@
         <v>11.44</v>
       </c>
       <c r="O16" t="n">
-        <v>61949155525</v>
+        <v>62624524625</v>
       </c>
       <c r="P16" t="n">
         <v>75900</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>312000</v>
+        <v>313500</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.59%</t>
+          <t>'-4.13%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>1.66</v>
       </c>
       <c r="E17" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F17" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G17" t="n">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="H17" t="n">
         <v>3.62</v>
@@ -1990,7 +1990,7 @@
         <v>1.96</v>
       </c>
       <c r="O17" t="n">
-        <v>70657171750</v>
+        <v>71388534000</v>
       </c>
       <c r="P17" t="n">
         <v>635000</v>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>26900</v>
+        <v>26750</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-28.07%</t>
+          <t>'-28.48%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.01</v>
       </c>
       <c r="E18" t="n">
-        <v>575</v>
+        <v>596</v>
       </c>
       <c r="F18" t="n">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="G18" t="n">
-        <v>1091</v>
+        <v>1143</v>
       </c>
       <c r="H18" t="n">
         <v>7.09</v>
@@ -2082,7 +2082,7 @@
         <v>7.08</v>
       </c>
       <c r="O18" t="n">
-        <v>70839450750</v>
+        <v>71679346400</v>
       </c>
       <c r="P18" t="n">
         <v>146600</v>

--- a/data/trending_integrated_20260921_11.xlsx
+++ b/data/trending_integrated_20260921_11.xlsx
@@ -578,13 +578,13 @@
         <v>-0.04</v>
       </c>
       <c r="E2" t="n">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="F2" t="n">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="G2" t="n">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="H2" t="n">
         <v>0.35</v>
@@ -610,7 +610,7 @@
         <v>0.39</v>
       </c>
       <c r="O2" t="n">
-        <v>201912589785</v>
+        <v>202143804035</v>
       </c>
       <c r="P2" t="n">
         <v>39350</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>美 타임 선정 '세계 최고 헬스테크 기업' 선정, 2주간의 폭락 후 반등 기대. 기관/외인 매수세 확인.</t>
+          <t>美 타임 선정 '세계 최고 헬스테크 기업' 선정 사실 기반의 강한 상승 기대감. 주포 및 기관/외인 프로그램 매수.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['헬스테크', '타임지', '반등']</t>
+          <t>['헬스테크', '타임지', '주포']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10820</v>
+        <v>10880</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+19.96%</t>
+          <t>'+20.62%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.09</v>
       </c>
       <c r="E3" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F3" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G3" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="H3" t="n">
         <v>8.6</v>
@@ -702,7 +702,7 @@
         <v>8.51</v>
       </c>
       <c r="O3" t="n">
-        <v>195383117490</v>
+        <v>199709450535</v>
       </c>
       <c r="P3" t="n">
         <v>11640</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5930</v>
+        <v>5890</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+9.21%</t>
+          <t>'+8.47%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.31</v>
       </c>
       <c r="E4" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G4" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H4" t="n">
         <v>0.19</v>
@@ -794,7 +794,7 @@
         <v>0.5</v>
       </c>
       <c r="O4" t="n">
-        <v>57928444150</v>
+        <v>58323324850</v>
       </c>
       <c r="P4" t="n">
         <v>13140</v>
@@ -839,83 +839,83 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11180</v>
+        <v>31400</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+6.27%</t>
+          <t>'+5.90%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.16</v>
+        <v>-0.48</v>
       </c>
       <c r="E5" t="n">
-        <v>82</v>
+        <v>327</v>
       </c>
       <c r="F5" t="n">
-        <v>55</v>
+        <v>206</v>
       </c>
       <c r="G5" t="n">
-        <v>164</v>
+        <v>1426</v>
       </c>
       <c r="H5" t="n">
-        <v>18.29</v>
+        <v>16.67</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>10520</v>
+        <v>29650</v>
       </c>
       <c r="K5" t="n">
-        <v>10780</v>
+        <v>30400</v>
       </c>
       <c r="L5" t="n">
-        <v>12190</v>
+        <v>33400</v>
       </c>
       <c r="M5" t="n">
-        <v>10590</v>
+        <v>29400</v>
       </c>
       <c r="N5" t="n">
-        <v>18.13</v>
+        <v>17.15</v>
       </c>
       <c r="O5" t="n">
-        <v>164409880460</v>
+        <v>23906157975</v>
       </c>
       <c r="P5" t="n">
-        <v>22450</v>
+        <v>69200</v>
       </c>
       <c r="Q5" t="n">
-        <v>1760</v>
+        <v>24150</v>
       </c>
       <c r="R5" t="n">
-        <v>-6000</v>
+        <v>-148000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-7000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>광통신주 미장 급등 및 나스닥 선물 상승 영향, 20% 상승 기대감. 거래량 부족, 개인 물량 털리는 구간 우려.</t>
+          <t>FDA 신약 승인 과정에서 제품명 조건부 수용 관련 내용, 리보세라닙 동일시 우려. 투자자 손실 관련 경고.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['광통신', '추세', '거래량']</t>
+          <t>['FDA', '신약 승인', '리보세라닙']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31400</v>
+        <v>11140</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+5.90%</t>
+          <t>'+5.89%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.48</v>
+        <v>0.16</v>
       </c>
       <c r="E6" t="n">
-        <v>316</v>
+        <v>86</v>
       </c>
       <c r="F6" t="n">
-        <v>201</v>
+        <v>59</v>
       </c>
       <c r="G6" t="n">
-        <v>1376</v>
+        <v>176</v>
       </c>
       <c r="H6" t="n">
-        <v>16.67</v>
+        <v>18.29</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>29650</v>
+        <v>10520</v>
       </c>
       <c r="K6" t="n">
-        <v>30400</v>
+        <v>10780</v>
       </c>
       <c r="L6" t="n">
-        <v>33400</v>
+        <v>12190</v>
       </c>
       <c r="M6" t="n">
-        <v>29400</v>
+        <v>10590</v>
       </c>
       <c r="N6" t="n">
-        <v>17.15</v>
+        <v>18.13</v>
       </c>
       <c r="O6" t="n">
-        <v>23349090225</v>
+        <v>165283114060</v>
       </c>
       <c r="P6" t="n">
-        <v>69200</v>
+        <v>22450</v>
       </c>
       <c r="Q6" t="n">
-        <v>24150</v>
+        <v>1760</v>
       </c>
       <c r="R6" t="n">
-        <v>-148000</v>
+        <v>-6000</v>
       </c>
       <c r="S6" t="n">
-        <v>-7000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>FDA 신약 승인 과정에서 제품명 조건부 수용 관련 내용, 리보세라닙 동일시 우려. 투자자 손실 관련 경고.</t>
+          <t>미국 광통신주 급등 관련 기대감. 차트 거래량 부족 지적.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['FDA', '신약 승인', '리보세라닙']</t>
+          <t>['광통신', 'RFHIC', '프리장']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>207000</v>
+        <v>207250</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+5.56%</t>
+          <t>'+5.69%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.09</v>
       </c>
       <c r="E7" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F7" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G7" t="n">
-        <v>245</v>
+        <v>261</v>
       </c>
       <c r="H7" t="n">
         <v>75.44</v>
@@ -1070,7 +1070,7 @@
         <v>75.53</v>
       </c>
       <c r="O7" t="n">
-        <v>489922807050</v>
+        <v>502416194800</v>
       </c>
       <c r="P7" t="n">
         <v>243500</v>
@@ -1133,10 +1133,10 @@
         <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="G8" t="n">
-        <v>2977</v>
+        <v>2807</v>
       </c>
       <c r="H8" t="n">
         <v>46.46</v>
@@ -1162,7 +1162,7 @@
         <v>46.48</v>
       </c>
       <c r="O8" t="n">
-        <v>2793244119750</v>
+        <v>2888937855500</v>
       </c>
       <c r="P8" t="n">
         <v>374500</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>내년 상반기 상승장 전망, 배당금 및 자사주 소각/배당 관련 기대감. 신한증권 시스템 먹통 관련 불만 제기.</t>
+          <t>배당 및 3분기 실적 발표 기대감. 신한증권 시스템 오류에 대한 불만.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['AI', '배당', '자사주']</t>
+          <t>['배당', '실적', '신한증권']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1870000</v>
+        <v>1867000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+0.70%</t>
+          <t>'+0.54%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="G9" t="n">
-        <v>2796</v>
+        <v>2638</v>
       </c>
       <c r="H9" t="n">
         <v>50.23</v>
@@ -1254,7 +1254,7 @@
         <v>50.1</v>
       </c>
       <c r="O9" t="n">
-        <v>2349422774000</v>
+        <v>2428578775500</v>
       </c>
       <c r="P9" t="n">
         <v>2987000</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미선물 및 반도체주 급등, 20일선 위로 상승 추세 전환 기대. 3분기 및 연간 영업이익 증대 전망.</t>
+          <t>미국 선물 및 반도체 주가 급등에 따른 SK하이닉스 상승 기대. 9월 수출 호조 전망.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['반도체', 'AI', '추세']</t>
+          <t>['반도체', '수출', '미선물']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>26550</v>
+        <v>26850</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-0.93%</t>
+          <t>'+0.19%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.3</v>
       </c>
       <c r="E10" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F10" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G10" t="n">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="H10" t="n">
         <v>2.11</v>
@@ -1346,7 +1346,7 @@
         <v>2.41</v>
       </c>
       <c r="O10" t="n">
-        <v>102480519425</v>
+        <v>103569047375</v>
       </c>
       <c r="P10" t="n">
         <v>59600</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4160</v>
+        <v>4180</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-1.42%</t>
+          <t>'-0.95%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.22</v>
       </c>
       <c r="E11" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G11" t="n">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="H11" t="n">
         <v>0.33</v>
@@ -1438,7 +1438,7 @@
         <v>0.55</v>
       </c>
       <c r="O11" t="n">
-        <v>26654188343</v>
+        <v>26808385127</v>
       </c>
       <c r="P11" t="n">
         <v>6480</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13660</v>
+        <v>13700</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.51%</t>
+          <t>'-1.23%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.58</v>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F12" t="n">
         <v>32</v>
       </c>
       <c r="G12" t="n">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="H12" t="n">
         <v>5.5</v>
@@ -1530,7 +1530,7 @@
         <v>4.92</v>
       </c>
       <c r="O12" t="n">
-        <v>58381367610</v>
+        <v>59019122710</v>
       </c>
       <c r="P12" t="n">
         <v>30200</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>78500</v>
+        <v>78700</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.88%</t>
+          <t>'-1.62%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.1</v>
       </c>
       <c r="E13" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F13" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G13" t="n">
-        <v>611</v>
+        <v>623</v>
       </c>
       <c r="H13" t="n">
         <v>10.58</v>
@@ -1622,7 +1622,7 @@
         <v>10.68</v>
       </c>
       <c r="O13" t="n">
-        <v>86445689350</v>
+        <v>87515056150</v>
       </c>
       <c r="P13" t="n">
         <v>184000</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>K-방산, 유럽 드론 시장 진출 기대감. 공매도 규제 및 숏커버링 통한 주가 상승 전망.</t>
+          <t>K-방산, 다층 대드론 시장 개척 관련 뉴스 기반 상승 기대. 공매도 금지 요구.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['K-방산', '드론', '공매도']</t>
+          <t>['방산', '드론', '공매도']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18420</v>
+        <v>18480</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-2.59%</t>
+          <t>'-2.27%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F14" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G14" t="n">
-        <v>258</v>
+        <v>281</v>
       </c>
       <c r="H14" t="n">
         <v>10.74</v>
@@ -1714,7 +1714,7 @@
         <v>10.74</v>
       </c>
       <c r="O14" t="n">
-        <v>57686796355</v>
+        <v>58879794830</v>
       </c>
       <c r="P14" t="n">
         <v>40350</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17610</v>
+        <v>17670</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.88%</t>
+          <t>'-3.55%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>3.29</v>
       </c>
       <c r="E15" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F15" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G15" t="n">
-        <v>780</v>
+        <v>804</v>
       </c>
       <c r="H15" t="n">
         <v>7.9</v>
@@ -1806,7 +1806,7 @@
         <v>4.61</v>
       </c>
       <c r="O15" t="n">
-        <v>172019865590</v>
+        <v>176455496000</v>
       </c>
       <c r="P15" t="n">
         <v>31500</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미국 광통신 AI주 급등세에 따른 연말/연초까지 상승 전망.</t>
+          <t>미국 광통신 및 AI주 급등에 따른 대한광통신 상승 기대. 기관 매수세 유입.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['광통신', 'AI주', '미국 시장']</t>
+          <t>['광통신', 'AI주', '기관매수']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1866,13 +1866,13 @@
         <v>0.48</v>
       </c>
       <c r="E16" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F16" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G16" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H16" t="n">
         <v>11.92</v>
@@ -1898,7 +1898,7 @@
         <v>11.44</v>
       </c>
       <c r="O16" t="n">
-        <v>62624524625</v>
+        <v>63268961725</v>
       </c>
       <c r="P16" t="n">
         <v>75900</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>313500</v>
+        <v>312000</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.13%</t>
+          <t>'-4.59%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>1.66</v>
       </c>
       <c r="E17" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F17" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G17" t="n">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="H17" t="n">
         <v>3.62</v>
@@ -1990,7 +1990,7 @@
         <v>1.96</v>
       </c>
       <c r="O17" t="n">
-        <v>71388534000</v>
+        <v>72231839000</v>
       </c>
       <c r="P17" t="n">
         <v>635000</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>가온전선, 금일 하락세 속 40만원 이상 돌파 전망. 외국인 매도 물량 출회 및 고평가 논란.</t>
+          <t>52주 신고가 돌파 및 40만원 이상 상승 전망. 외인 매수세 유입.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['하락', '돌파', '고평가']</t>
+          <t>['신고가', '외국인', '고평가']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>26750</v>
+        <v>26450</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-28.48%</t>
+          <t>'-29.28%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.01</v>
       </c>
       <c r="E18" t="n">
-        <v>596</v>
+        <v>622</v>
       </c>
       <c r="F18" t="n">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="G18" t="n">
-        <v>1143</v>
+        <v>1192</v>
       </c>
       <c r="H18" t="n">
         <v>7.09</v>
@@ -2082,7 +2082,7 @@
         <v>7.08</v>
       </c>
       <c r="O18" t="n">
-        <v>71679346400</v>
+        <v>73812812500</v>
       </c>
       <c r="P18" t="n">
         <v>146600</v>

--- a/data/trending_integrated_20260921_11.xlsx
+++ b/data/trending_integrated_20260921_11.xlsx
@@ -578,13 +578,13 @@
         <v>-0.04</v>
       </c>
       <c r="E2" t="n">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="F2" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G2" t="n">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="H2" t="n">
         <v>0.35</v>
@@ -610,7 +610,7 @@
         <v>0.39</v>
       </c>
       <c r="O2" t="n">
-        <v>202143804035</v>
+        <v>202333936535</v>
       </c>
       <c r="P2" t="n">
         <v>39350</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>美 타임 선정 '세계 최고 헬스테크 기업' 선정 사실 기반의 강한 상승 기대감. 주포 및 기관/외인 프로그램 매수.</t>
+          <t>美 타임지 선정 '세계 최고 헬스테크 기업' 관련 뉴스. 기관, 외국인 프로그램 매수 확인.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['헬스테크', '타임지', '주포']</t>
+          <t>['헬스테크', '타임지', '기관']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,21 +659,21 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10880</v>
+        <v>10730</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+20.62%</t>
+          <t>'+18.96%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.09</v>
       </c>
       <c r="E3" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F3" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G3" t="n">
         <v>190</v>
@@ -702,7 +702,7 @@
         <v>8.51</v>
       </c>
       <c r="O3" t="n">
-        <v>199709450535</v>
+        <v>206051411505</v>
       </c>
       <c r="P3" t="n">
         <v>11640</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5890</v>
+        <v>5880</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+8.47%</t>
+          <t>'+8.29%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.31</v>
       </c>
       <c r="E4" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F4" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G4" t="n">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="H4" t="n">
         <v>0.19</v>
@@ -794,7 +794,7 @@
         <v>0.5</v>
       </c>
       <c r="O4" t="n">
-        <v>58323324850</v>
+        <v>58591086920</v>
       </c>
       <c r="P4" t="n">
         <v>13140</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31400</v>
+        <v>31700</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+5.90%</t>
+          <t>'+6.91%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.48</v>
       </c>
       <c r="E5" t="n">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="F5" t="n">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="G5" t="n">
-        <v>1426</v>
+        <v>1466</v>
       </c>
       <c r="H5" t="n">
         <v>16.67</v>
@@ -886,7 +886,7 @@
         <v>17.15</v>
       </c>
       <c r="O5" t="n">
-        <v>23906157975</v>
+        <v>24433336625</v>
       </c>
       <c r="P5" t="n">
         <v>69200</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11140</v>
+        <v>11130</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+5.89%</t>
+          <t>'+5.80%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.16</v>
       </c>
       <c r="E6" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F6" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G6" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H6" t="n">
         <v>18.29</v>
@@ -978,7 +978,7 @@
         <v>18.13</v>
       </c>
       <c r="O6" t="n">
-        <v>165283114060</v>
+        <v>166299061780</v>
       </c>
       <c r="P6" t="n">
         <v>22450</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>207250</v>
+        <v>207000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+5.69%</t>
+          <t>'+5.56%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.09</v>
       </c>
       <c r="E7" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F7" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G7" t="n">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="H7" t="n">
         <v>75.44</v>
@@ -1070,7 +1070,7 @@
         <v>75.53</v>
       </c>
       <c r="O7" t="n">
-        <v>502416194800</v>
+        <v>509925549300</v>
       </c>
       <c r="P7" t="n">
         <v>243500</v>
@@ -1133,10 +1133,10 @@
         <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="G8" t="n">
-        <v>2807</v>
+        <v>2779</v>
       </c>
       <c r="H8" t="n">
         <v>46.46</v>
@@ -1162,7 +1162,7 @@
         <v>46.48</v>
       </c>
       <c r="O8" t="n">
-        <v>2888937855500</v>
+        <v>2979964903250</v>
       </c>
       <c r="P8" t="n">
         <v>374500</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>배당 및 3분기 실적 발표 기대감. 신한증권 시스템 오류에 대한 불만.</t>
+          <t>신한증권 시스템 오류 관련 언급 다수. 배당락일 및 실적 발표 관련 기대감 존재.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['배당', '실적', '신한증권']</t>
+          <t>['배당', '실적 발표', '신한증권']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="G9" t="n">
-        <v>2638</v>
+        <v>2550</v>
       </c>
       <c r="H9" t="n">
         <v>50.23</v>
@@ -1254,7 +1254,7 @@
         <v>50.1</v>
       </c>
       <c r="O9" t="n">
-        <v>2428578775500</v>
+        <v>2484141097000</v>
       </c>
       <c r="P9" t="n">
         <v>2987000</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 선물 및 반도체 주가 급등에 따른 SK하이닉스 상승 기대. 9월 수출 호조 전망.</t>
+          <t>미국 증시 및 반도체 관련주 급등에 따른 상승 기대감. 신한증권 시스템 오류 관련 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['반도체', '수출', '미선물']</t>
+          <t>['반도체', '미국 증시', '신한증권']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1317,10 +1317,10 @@
         <v>44</v>
       </c>
       <c r="F10" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G10" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H10" t="n">
         <v>2.11</v>
@@ -1346,7 +1346,7 @@
         <v>2.41</v>
       </c>
       <c r="O10" t="n">
-        <v>103569047375</v>
+        <v>104492125450</v>
       </c>
       <c r="P10" t="n">
         <v>59600</v>
@@ -1406,13 +1406,13 @@
         <v>-0.22</v>
       </c>
       <c r="E11" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F11" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G11" t="n">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="H11" t="n">
         <v>0.33</v>
@@ -1438,7 +1438,7 @@
         <v>0.55</v>
       </c>
       <c r="O11" t="n">
-        <v>26808385127</v>
+        <v>27029886557</v>
       </c>
       <c r="P11" t="n">
         <v>6480</v>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13700</v>
+        <v>13680</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.23%</t>
+          <t>'-1.37%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1504,7 +1504,7 @@
         <v>32</v>
       </c>
       <c r="G12" t="n">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="H12" t="n">
         <v>5.5</v>
@@ -1530,7 +1530,7 @@
         <v>4.92</v>
       </c>
       <c r="O12" t="n">
-        <v>59019122710</v>
+        <v>59608153245</v>
       </c>
       <c r="P12" t="n">
         <v>30200</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>78700</v>
+        <v>78600</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.62%</t>
+          <t>'-1.75%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.1</v>
       </c>
       <c r="E13" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F13" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G13" t="n">
-        <v>623</v>
+        <v>637</v>
       </c>
       <c r="H13" t="n">
         <v>10.58</v>
@@ -1622,7 +1622,7 @@
         <v>10.68</v>
       </c>
       <c r="O13" t="n">
-        <v>87515056150</v>
+        <v>88568639650</v>
       </c>
       <c r="P13" t="n">
         <v>184000</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>K-방산, 다층 대드론 시장 개척 관련 뉴스 기반 상승 기대. 공매도 금지 요구.</t>
+          <t>K-방산, 드론 관련 뉴스 긍정적. 공매도 관련 언급 및 8만원 회복 기대.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['방산', '드론', '공매도']</t>
+          <t>['K-방산', '드론', '공매도']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18480</v>
+        <v>18500</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-2.27%</t>
+          <t>'-2.17%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F14" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G14" t="n">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="H14" t="n">
         <v>10.74</v>
@@ -1714,7 +1714,7 @@
         <v>10.74</v>
       </c>
       <c r="O14" t="n">
-        <v>58879794830</v>
+        <v>60095202835</v>
       </c>
       <c r="P14" t="n">
         <v>40350</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17670</v>
+        <v>17740</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.55%</t>
+          <t>'-3.17%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>3.29</v>
       </c>
       <c r="E15" t="n">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="F15" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G15" t="n">
-        <v>804</v>
+        <v>813</v>
       </c>
       <c r="H15" t="n">
         <v>7.9</v>
@@ -1806,7 +1806,7 @@
         <v>4.61</v>
       </c>
       <c r="O15" t="n">
-        <v>176455496000</v>
+        <v>178929266460</v>
       </c>
       <c r="P15" t="n">
         <v>31500</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미국 광통신 및 AI주 급등에 따른 대한광통신 상승 기대. 기관 매수세 유입.</t>
+          <t>미국 광통신주 및 AI 관련주 급등에 따른 기대감. 연말, 연초까지 긍정적 전망.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['광통신', 'AI주', '기관매수']</t>
+          <t>['광통신', 'AI', '미국 증시']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>30150</v>
+        <v>30050</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.13%</t>
+          <t>'-4.45%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.48</v>
       </c>
       <c r="E16" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F16" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G16" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H16" t="n">
         <v>11.92</v>
@@ -1898,7 +1898,7 @@
         <v>11.44</v>
       </c>
       <c r="O16" t="n">
-        <v>63268961725</v>
+        <v>65627928400</v>
       </c>
       <c r="P16" t="n">
         <v>75900</v>
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>312000</v>
+        <v>311500</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.59%</t>
+          <t>'-4.74%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1964,7 +1964,7 @@
         <v>71</v>
       </c>
       <c r="G17" t="n">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="H17" t="n">
         <v>3.62</v>
@@ -1990,7 +1990,7 @@
         <v>1.96</v>
       </c>
       <c r="O17" t="n">
-        <v>72231839000</v>
+        <v>73270811000</v>
       </c>
       <c r="P17" t="n">
         <v>635000</v>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>26450</v>
+        <v>27150</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-29.28%</t>
+          <t>'-27.41%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.01</v>
       </c>
       <c r="E18" t="n">
-        <v>622</v>
+        <v>630</v>
       </c>
       <c r="F18" t="n">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="G18" t="n">
-        <v>1192</v>
+        <v>1195</v>
       </c>
       <c r="H18" t="n">
         <v>7.09</v>
@@ -2082,7 +2082,7 @@
         <v>7.08</v>
       </c>
       <c r="O18" t="n">
-        <v>73812812500</v>
+        <v>75116195800</v>
       </c>
       <c r="P18" t="n">
         <v>146600</v>

--- a/data/trending_integrated_20260921_11.xlsx
+++ b/data/trending_integrated_20260921_11.xlsx
@@ -578,13 +578,13 @@
         <v>-0.04</v>
       </c>
       <c r="E2" t="n">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="F2" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G2" t="n">
-        <v>281</v>
+        <v>301</v>
       </c>
       <c r="H2" t="n">
         <v>0.35</v>
@@ -610,7 +610,7 @@
         <v>0.39</v>
       </c>
       <c r="O2" t="n">
-        <v>202333936535</v>
+        <v>203032376785</v>
       </c>
       <c r="P2" t="n">
         <v>39350</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>美 타임지 선정 '세계 최고 헬스테크 기업' 관련 뉴스. 기관, 외국인 프로그램 매수 확인.</t>
+          <t>미국 타임지 선정 '세계 최고 헬스테크 기업' 그룹 포함으로 인한 높은 기대감. 단기 급등 후 개인 물량 털기 가능성.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['헬스테크', '타임지', '기관']</t>
+          <t>['헬스테크', '타임지', '선정']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>0.09</v>
       </c>
       <c r="E3" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F3" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G3" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="H3" t="n">
         <v>8.6</v>
@@ -702,7 +702,7 @@
         <v>8.51</v>
       </c>
       <c r="O3" t="n">
-        <v>206051411505</v>
+        <v>210574104805</v>
       </c>
       <c r="P3" t="n">
         <v>11640</v>
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5880</v>
+        <v>5870</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+8.29%</t>
+          <t>'+8.10%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -768,7 +768,7 @@
         <v>31</v>
       </c>
       <c r="G4" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="H4" t="n">
         <v>0.19</v>
@@ -794,7 +794,7 @@
         <v>0.5</v>
       </c>
       <c r="O4" t="n">
-        <v>58591086920</v>
+        <v>58810788840</v>
       </c>
       <c r="P4" t="n">
         <v>13140</v>
@@ -854,13 +854,13 @@
         <v>-0.48</v>
       </c>
       <c r="E5" t="n">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="F5" t="n">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="G5" t="n">
-        <v>1466</v>
+        <v>1498</v>
       </c>
       <c r="H5" t="n">
         <v>16.67</v>
@@ -886,7 +886,7 @@
         <v>17.15</v>
       </c>
       <c r="O5" t="n">
-        <v>24433336625</v>
+        <v>24706932750</v>
       </c>
       <c r="P5" t="n">
         <v>69200</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11130</v>
+        <v>11110</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+5.80%</t>
+          <t>'+5.61%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.16</v>
       </c>
       <c r="E6" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F6" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G6" t="n">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="H6" t="n">
         <v>18.29</v>
@@ -978,7 +978,7 @@
         <v>18.13</v>
       </c>
       <c r="O6" t="n">
-        <v>166299061780</v>
+        <v>167415690815</v>
       </c>
       <c r="P6" t="n">
         <v>22450</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>미국 광통신주 급등 관련 기대감. 차트 거래량 부족 지적.</t>
+          <t>미국 광통신주 급등과 선물 지수 상승에 따른 투자 심리 개선. 단기 급등 가능성 및 개인 투자자 털기 구간 경계.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['광통신', 'RFHIC', '프리장']</t>
+          <t>['광통신', '선물', '추세']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1038,13 +1038,13 @@
         <v>-0.09</v>
       </c>
       <c r="E7" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F7" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G7" t="n">
-        <v>271</v>
+        <v>289</v>
       </c>
       <c r="H7" t="n">
         <v>75.44</v>
@@ -1070,7 +1070,7 @@
         <v>75.53</v>
       </c>
       <c r="O7" t="n">
-        <v>509925549300</v>
+        <v>518181547050</v>
       </c>
       <c r="P7" t="n">
         <v>243500</v>
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>272000</v>
+        <v>272500</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.21%</t>
+          <t>'+4.41%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1133,10 +1133,10 @@
         <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="G8" t="n">
-        <v>2779</v>
+        <v>2735</v>
       </c>
       <c r="H8" t="n">
         <v>46.46</v>
@@ -1153,7 +1153,7 @@
         <v>264000</v>
       </c>
       <c r="L8" t="n">
-        <v>272500</v>
+        <v>273000</v>
       </c>
       <c r="M8" t="n">
         <v>263500</v>
@@ -1162,7 +1162,7 @@
         <v>46.48</v>
       </c>
       <c r="O8" t="n">
-        <v>2979964903250</v>
+        <v>3112843191000</v>
       </c>
       <c r="P8" t="n">
         <v>374500</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>신한증권 시스템 오류 관련 언급 다수. 배당락일 및 실적 발표 관련 기대감 존재.</t>
+          <t>신한증권 시스템 오류로 인한 투자자 불편 발생. 3분기 실적 발표 및 자사주 소각, 배당 예정으로 인한 기대감.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['배당', '실적 발표', '신한증권']</t>
+          <t>['실적', '배당', '자사주']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1867000</v>
+        <v>1871000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+0.54%</t>
+          <t>'+0.75%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="G9" t="n">
-        <v>2550</v>
+        <v>2420</v>
       </c>
       <c r="H9" t="n">
         <v>50.23</v>
@@ -1254,7 +1254,7 @@
         <v>50.1</v>
       </c>
       <c r="O9" t="n">
-        <v>2484141097000</v>
+        <v>2565382577500</v>
       </c>
       <c r="P9" t="n">
         <v>2987000</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 증시 및 반도체 관련주 급등에 따른 상승 기대감. 신한증권 시스템 오류 관련 언급.</t>
+          <t>미국 선물 시장 급등 및 반도체 섹터 강세에 따른 긍정적 전망. 신한증권 앱 오류로 인한 거래 불편.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['반도체', '미국 증시', '신한증권']</t>
+          <t>['반도체', '수출', '선물']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>26850</v>
+        <v>26700</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.19%</t>
+          <t>'-0.37%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.3</v>
       </c>
       <c r="E10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F10" t="n">
         <v>36</v>
       </c>
       <c r="G10" t="n">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="H10" t="n">
         <v>2.11</v>
@@ -1346,7 +1346,7 @@
         <v>2.41</v>
       </c>
       <c r="O10" t="n">
-        <v>104492125450</v>
+        <v>105319346975</v>
       </c>
       <c r="P10" t="n">
         <v>59600</v>
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4180</v>
+        <v>13745</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-0.95%</t>
+          <t>'-0.90%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.22</v>
+        <v>0.58</v>
       </c>
       <c r="E11" t="n">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="F11" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="G11" t="n">
-        <v>230</v>
+        <v>303</v>
       </c>
       <c r="H11" t="n">
-        <v>0.33</v>
+        <v>5.5</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,38 +1423,38 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>4220</v>
+        <v>13870</v>
       </c>
       <c r="K11" t="n">
-        <v>4220</v>
+        <v>14070</v>
       </c>
       <c r="L11" t="n">
-        <v>4415</v>
+        <v>14790</v>
       </c>
       <c r="M11" t="n">
-        <v>4105</v>
+        <v>13610</v>
       </c>
       <c r="N11" t="n">
-        <v>0.55</v>
+        <v>4.92</v>
       </c>
       <c r="O11" t="n">
-        <v>27029886557</v>
+        <v>60104413915</v>
       </c>
       <c r="P11" t="n">
-        <v>6480</v>
+        <v>30200</v>
       </c>
       <c r="Q11" t="n">
-        <v>1738</v>
+        <v>3540</v>
       </c>
       <c r="R11" t="n">
-        <v>208000</v>
+        <v>-298000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-7000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미투온, 미버스 관련 코인주 동반 상승 속 거래량 부진 및 재료 소멸 우려. 매도 물량 출회 가능성.</t>
+          <t>원전 관련 기대감 언급. 신한투자증권의 공매도 의혹 및 주가 하락에 대한 불만.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['미버스', '거래량', '재료소멸']</t>
+          <t>['원전', '신한투자증권', '공매도']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,77 +1476,77 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13680</v>
+        <v>18590</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.37%</t>
+          <t>'-1.69%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.58</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="F12" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="G12" t="n">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="H12" t="n">
-        <v>5.5</v>
+        <v>10.74</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>13870</v>
+        <v>18910</v>
       </c>
       <c r="K12" t="n">
-        <v>14070</v>
+        <v>19050</v>
       </c>
       <c r="L12" t="n">
-        <v>14790</v>
+        <v>19050</v>
       </c>
       <c r="M12" t="n">
-        <v>13610</v>
+        <v>18090</v>
       </c>
       <c r="N12" t="n">
-        <v>4.92</v>
+        <v>10.74</v>
       </c>
       <c r="O12" t="n">
-        <v>59608153245</v>
+        <v>61827350715</v>
       </c>
       <c r="P12" t="n">
-        <v>30200</v>
+        <v>40350</v>
       </c>
       <c r="Q12" t="n">
-        <v>3540</v>
+        <v>3320</v>
       </c>
       <c r="R12" t="n">
-        <v>-298000</v>
+        <v>-673000</v>
       </c>
       <c r="S12" t="n">
-        <v>-7000</v>
+        <v>-88000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>원전 관련 기대감 언급. 신한투자증권의 공매도 의혹 및 주가 하락에 대한 불만.</t>
+          <t>대우건설, 공매도 장부 조작 의혹 및 대차해지 운동 동참 호소. 주가 하락 추세 및 기관 매매 관련 논의.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['원전', '신한투자증권', '공매도']</t>
+          <t>['공매도', '대차해지', '추세']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1590,13 +1590,13 @@
         <v>-0.1</v>
       </c>
       <c r="E13" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F13" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G13" t="n">
-        <v>637</v>
+        <v>665</v>
       </c>
       <c r="H13" t="n">
         <v>10.58</v>
@@ -1622,7 +1622,7 @@
         <v>10.68</v>
       </c>
       <c r="O13" t="n">
-        <v>88568639650</v>
+        <v>89567638600</v>
       </c>
       <c r="P13" t="n">
         <v>184000</v>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>K-방산, 드론 관련 뉴스 긍정적. 공매도 관련 언급 및 8만원 회복 기대.</t>
+          <t>K-방산의 다층 대드론 시장 진입 기대감. 공매도 세력과의 공방 및 8만 원 회복 시 추가 상승 전망.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['K-방산', '드론', '공매도']</t>
+          <t>['방산', '드론', '공매도']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1667,70 +1667,70 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18500</v>
+        <v>4130</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-2.17%</t>
+          <t>'-2.13%</t>
         </is>
       </c>
       <c r="D14" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="E14" t="n">
+        <v>73</v>
+      </c>
+      <c r="F14" t="n">
+        <v>45</v>
+      </c>
+      <c r="G14" t="n">
+        <v>225</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>4220</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4220</v>
+      </c>
+      <c r="L14" t="n">
+        <v>4415</v>
+      </c>
+      <c r="M14" t="n">
+        <v>4105</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O14" t="n">
+        <v>27237982302</v>
+      </c>
+      <c r="P14" t="n">
+        <v>6480</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1738</v>
+      </c>
+      <c r="R14" t="n">
+        <v>208000</v>
+      </c>
+      <c r="S14" t="n">
         <v>0</v>
       </c>
-      <c r="E14" t="n">
-        <v>75</v>
-      </c>
-      <c r="F14" t="n">
-        <v>50</v>
-      </c>
-      <c r="G14" t="n">
-        <v>294</v>
-      </c>
-      <c r="H14" t="n">
-        <v>10.74</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>MarketType.KOSPI</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>18910</v>
-      </c>
-      <c r="K14" t="n">
-        <v>19050</v>
-      </c>
-      <c r="L14" t="n">
-        <v>19050</v>
-      </c>
-      <c r="M14" t="n">
-        <v>18090</v>
-      </c>
-      <c r="N14" t="n">
-        <v>10.74</v>
-      </c>
-      <c r="O14" t="n">
-        <v>60095202835</v>
-      </c>
-      <c r="P14" t="n">
-        <v>40350</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3320</v>
-      </c>
-      <c r="R14" t="n">
-        <v>-673000</v>
-      </c>
-      <c r="S14" t="n">
-        <v>-88000</v>
-      </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>대우건설, 공매도 장부 조작 의혹 및 대차해지 운동 동참 호소. 주가 하락 추세 및 기관 매매 관련 논의.</t>
+          <t>미투온, 미버스 관련 코인주 동반 상승 속 거래량 부진 및 재료 소멸 우려. 매도 물량 출회 가능성.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,11 +1739,11 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['공매도', '대차해지', '추세']</t>
+          <t>['미버스', '거래량', '재료소멸']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>201490</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17740</v>
+        <v>17750</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.17%</t>
+          <t>'-3.11%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>3.29</v>
       </c>
       <c r="E15" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F15" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G15" t="n">
-        <v>813</v>
+        <v>824</v>
       </c>
       <c r="H15" t="n">
         <v>7.9</v>
@@ -1806,7 +1806,7 @@
         <v>4.61</v>
       </c>
       <c r="O15" t="n">
-        <v>178929266460</v>
+        <v>180630535405</v>
       </c>
       <c r="P15" t="n">
         <v>31500</v>
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>30050</v>
+        <v>30200</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.45%</t>
+          <t>'-3.97%</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1872,7 +1872,7 @@
         <v>42</v>
       </c>
       <c r="G16" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="H16" t="n">
         <v>11.92</v>
@@ -1898,7 +1898,7 @@
         <v>11.44</v>
       </c>
       <c r="O16" t="n">
-        <v>65627928400</v>
+        <v>66599632875</v>
       </c>
       <c r="P16" t="n">
         <v>75900</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>311500</v>
+        <v>312000</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.74%</t>
+          <t>'-4.59%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>1.66</v>
       </c>
       <c r="E17" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F17" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G17" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="H17" t="n">
         <v>3.62</v>
@@ -1990,7 +1990,7 @@
         <v>1.96</v>
       </c>
       <c r="O17" t="n">
-        <v>73270811000</v>
+        <v>73873254750</v>
       </c>
       <c r="P17" t="n">
         <v>635000</v>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>27150</v>
+        <v>27750</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-27.41%</t>
+          <t>'-25.80%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.01</v>
       </c>
       <c r="E18" t="n">
-        <v>630</v>
+        <v>637</v>
       </c>
       <c r="F18" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G18" t="n">
-        <v>1195</v>
+        <v>1204</v>
       </c>
       <c r="H18" t="n">
         <v>7.09</v>
@@ -2082,7 +2082,7 @@
         <v>7.08</v>
       </c>
       <c r="O18" t="n">
-        <v>75116195800</v>
+        <v>76840061725</v>
       </c>
       <c r="P18" t="n">
         <v>146600</v>
